--- a/stories/arbres/TREE-SOC-006.xlsx
+++ b/stories/arbres/TREE-SOC-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules est au marché, avec papa. Des tomates brillent. Papa dit : tu peux aider. Une tâche sûre, avec un adulte. Jules lave une tomate sous l'eau, plus tard à la maison. Jules pose une cuillère. Jules apporte le pain. Laver. Poser. Apporter. Avec un adulte. Une tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+          <t>Jules est au marché, avec papa. Des tomates brillent. Tu peux aider. Une tâche sûre, avec un adulte. Jules lave une tomate sous l'eau, plus tard à la maison. Jules pose une cuillère. Jules apporte le pain. Laver. Poser. Apporter. Avec un adulte. Une tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules est au marché, avec papa. Des tomates brillent.
+papa|Tu peux aider.
+narrateur|Une tâche sûre, avec un adulte. Jules lave une tomate sous l'eau, plus tard à la maison. Jules pose une cuillère. Jules apporte le pain. Laver. Poser. Apporter. Avec un adulte. Une tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1515,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1544,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint Tom. Tom tient un panier. Papa dit : tâche sûre, avec un adulte. Jules pose une pomme dans le panier. Poser. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+          <t>Jules rejoint Tom. Tom tient un panier. Tâche sûre, avec un adulte. Jules pose une pomme dans le panier. Poser. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1682,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Tom. Tom tient un panier.
+papa|Tâche sûre, avec un adulte.
+narrateur|Jules pose une pomme dans le panier. Poser. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On aide. On fait une quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a fait une tâche sûre, avec un adulte. Laver, poser, apporter. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2229,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2396,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend les cubes. Un vélo passe, toc toc. Les cubes attendent. D'abord, Jules pose la cuillère. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2587,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. La lumière est claire. On met le manteau. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Des miettes dorment sur la table. On boit une gorgée. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un chat miaule une fois. On feuillette le livre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3756,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend le livre. Un ballon frotte le sol. Le livre est fermé. Jules apporte le pain. Avec un adulte. Tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3976,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules pose une pomme près de l'assiette. Les chaussures font toc toc. On referme le livre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. Papa dit : c'est bien.</t>
+          <t>Jules pose une pomme près de l'assiette. Les chaussures font toc toc. On referme le livre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4114,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Les chaussures font toc toc. On referme le livre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4282,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4449,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. La couverture est douce. On pose le ballon. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4616,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4783,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Une cloche tinte au loin. On secoue le sable. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4950,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5117,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend la dînette. Le sol est un peu frais. La dînette imite. Jules lave une tomate imaginaire. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5308,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5475,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Le bois sent le chaud. On caresse le tissu. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5642,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5809,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Une goutte tombe, ploc. On tend la main. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5976,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6143,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le savon sent la fleur. On chante un petit air. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6310,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6477,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Léa. Léa sourit. Jules apporte le pain à papa. Apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6662,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On lave la tomate. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6835,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Le pain est sur la table. Tâche sûre. Avec papa. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7026,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7193,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend les cubes. Une cuillère tinte. Jules empile, puis pose une nappe. Tâche sûre. Avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7384,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7211,7 +7413,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules pose une pomme près de l'assiette. Le tissu est tout doux. On compte jusqu'à trois. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. Papa dit : c'est bien.</t>
+          <t>Jules pose une pomme près de l'assiette. Le tissu est tout doux. On compte jusqu'à trois. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7349,6 +7551,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Le tissu est tout doux. On compte jusqu'à trois. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7719,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7886,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Une cuillère tinte. On montre du doigt. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8053,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8220,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le sable est tiède. On range la chaise. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8387,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8554,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend le livre. Le sol est un peu frais. Jules montre une image de pain. Apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8745,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8912,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Un rire court, tout petit. On range un objet. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9079,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9246,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Le papier froisse, chut. On se tient la main. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9413,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9580,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. L'herbe chatouille le mollet. On dit merci. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9747,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9914,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend la dînette. Un oiseau chante tout près. Une petite assiette. Jules pose. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10105,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10134,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules pose une pomme près de l'assiette. Un pigeon roucoule. On souffle doucement. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. Papa dit : c'est bien.</t>
+          <t>Jules pose une pomme près de l'assiette. Un pigeon roucoule. On souffle doucement. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10272,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Un pigeon roucoule. On souffle doucement. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. La fenêtre vibre un peu. On écoute jusqu'au bout. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10941,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le lait est froid dans le verre. On attend son tour. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11108,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11275,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint Sami. Sami montre une tomate. Plus tard, Jules la lavera. Laver. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11460,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Apporter le pain. C'est une tâche. ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11633,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La tomate est propre. Avec un adulte. Tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11824,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11991,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend les cubes. Le sol est un peu frais. Les cubes sont rangés. Jules lave les mains, avec papa. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12182,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12349,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. La corde du sac est rêche. On sourit ensemble. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12516,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12683,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Le savon mousse entre les doigts. On pose les pieds par terre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12850,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13017,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un ruisseau chante. On parle tout bas. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13184,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12839,7 +13213,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Jules prend le livre. Le savon mousse entre les doigts. Le livre sent le papier. Papa dit : encore une tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+          <t>Jules prend le livre. Le savon mousse entre les doigts. Le livre sent le papier. Encore une tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12977,6 +13351,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend le livre. Le savon mousse entre les doigts. Le livre sent le papier.
+papa|Encore une tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13543,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13572,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules pose une pomme près de l'assiette. La laine gratte un peu. On range les jouets. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. Papa dit : c'est bien.</t>
+          <t>Jules pose une pomme près de l'assiette. La laine gratte un peu. On range les jouets. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13710,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. La laine gratte un peu. On range les jouets. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13878,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14045,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Un pain croustille. On s'assoit un moment. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14212,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14379,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le savon glisse. On respire, un, deux. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14546,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14713,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules prend la dînette. Un vélo passe, toc toc. Jules range la dînette. Laver, poser, apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15071,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose une pomme près de l'assiette. Une plume vole. On referme le sac. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15238,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15405,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un yaourt près de l'assiette. Le banc est lisse. On essuie une miette. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15572,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15739,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un grelot sonne. On met le doudou près. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15906,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15946,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>ch1: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-006.xlsx
+++ b/stories/arbres/TREE-SOC-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Une tâche sûre, avec un adulte. Jules lave une tomate sous l'eau, plus tard à la maison. Jules pose une cuillère. Jules apporte le pain. Laver. Poser. Apporter. Avec un adulte. Une tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1520,6 +1526,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1689,6 +1696,7 @@
 narrateur|Jules pose une pomme dans le panier. Poser. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|On aide. On fait une quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Jules a fait une tâche sûre, avec un adulte. Laver, poser, apporter. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2234,6 +2244,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2401,6 +2412,7 @@
           <t>narrateur|Jules prend les cubes. Un vélo passe, toc toc. Les cubes attendent. D'abord, Jules pose la cuillère. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2604,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
           <t>narrateur|Jules pose une pomme près de l'assiette. La lumière est claire. On met le manteau. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3108,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Des miettes dorment sur la table. On boit une gorgée. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3444,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un chat miaule une fois. On feuillette le livre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3780,7 @@
           <t>narrateur|Jules prend le livre. Un ballon frotte le sol. Le livre est fermé. Jules apporte le pain. Avec un adulte. Tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3952,6 +3972,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4120,6 +4141,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4287,6 +4309,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4454,6 +4477,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. La couverture est douce. On pose le ballon. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4621,6 +4645,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4788,6 +4813,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Une cloche tinte au loin. On secoue le sable. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4955,6 +4981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5149,7 @@
           <t>narrateur|Jules prend la dînette. Le sol est un peu frais. La dînette imite. Jules lave une tomate imaginaire. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5313,6 +5341,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5480,6 +5509,7 @@
           <t>narrateur|Jules pose une pomme près de l'assiette. Le bois sent le chaud. On caresse le tissu. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5845,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Une goutte tombe, ploc. On tend la main. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6181,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le savon sent la fleur. On chante un petit air. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6349,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6517,7 @@
           <t>narrateur|Jules rejoint Léa. Léa sourit. Jules apporte le pain à papa. Apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6669,6 +6705,7 @@
           <t>narrateur|On lave la tomate. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6840,6 +6877,7 @@
           <t>narrateur|Le pain est sur la table. Tâche sûre. Avec papa. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7031,6 +7069,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7198,6 +7237,7 @@
           <t>narrateur|Jules prend les cubes. Une cuillère tinte. Jules empile, puis pose une nappe. Tâche sûre. Avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7389,6 +7429,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7557,6 +7598,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7724,6 +7766,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7891,6 +7934,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Une cuillère tinte. On montre du doigt. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8058,6 +8102,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8225,6 +8270,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le sable est tiède. On range la chaise. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8392,6 +8438,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8559,6 +8606,7 @@
           <t>narrateur|Jules prend le livre. Le sol est un peu frais. Jules montre une image de pain. Apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8750,6 +8798,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8917,6 +8966,7 @@
           <t>narrateur|Jules pose une pomme près de l'assiette. Un rire court, tout petit. On range un objet. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9084,6 +9134,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9251,6 +9302,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Le papier froisse, chut. On se tient la main. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9418,6 +9470,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9585,6 +9638,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. L'herbe chatouille le mollet. On dit merci. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9752,6 +9806,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9919,6 +9974,7 @@
           <t>narrateur|Jules prend la dînette. Un oiseau chante tout près. Une petite assiette. Jules pose. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10110,6 +10166,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10278,6 +10335,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10671,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. La fenêtre vibre un peu. On écoute jusqu'au bout. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10946,6 +11007,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le lait est froid dans le verre. On attend son tour. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11113,6 +11175,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11280,6 +11343,7 @@
           <t>narrateur|Jules rejoint Sami. Sami montre une tomate. Plus tard, Jules la lavera. Laver. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11467,6 +11531,7 @@
           <t>narrateur|Apporter le pain. C'est une tâche. ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11638,6 +11703,7 @@
           <t>narrateur|La tomate est propre. Avec un adulte. Tâche sûre. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11829,6 +11895,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11996,6 +12063,7 @@
           <t>narrateur|Jules prend les cubes. Le sol est un peu frais. Les cubes sont rangés. Jules lave les mains, avec papa. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12187,6 +12255,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12354,6 +12423,7 @@
           <t>narrateur|Jules pose une pomme près de l'assiette. La corde du sac est rêche. On sourit ensemble. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12521,6 +12591,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12688,6 +12759,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Le savon mousse entre les doigts. On pose les pieds par terre. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12855,6 +12927,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13022,6 +13095,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un ruisseau chante. On parle tout bas. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13189,6 +13263,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13357,6 +13432,7 @@
 papa|Encore une tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13548,6 +13624,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13716,6 +13793,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13883,6 +13961,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14050,6 +14129,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Un pain croustille. On s'assoit un moment. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. On souffle. Jules sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14217,6 +14297,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14384,6 +14465,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Le savon glisse. On respire, un, deux. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. L'adulte a dit merci. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14551,6 +14633,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14718,6 +14801,7 @@
           <t>narrateur|Jules prend la dînette. Un vélo passe, toc toc. Jules range la dînette. Laver, poser, apporter. Tâche sûre, avec un adulte. On fait une tâche sûre, avec un adulte. Laver, poser, apporter.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14909,6 +14993,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15076,6 +15161,7 @@
           <t>narrateur|Jules pose une pomme près de l'assiette. Une plume vole. On referme le sac. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La tomate est lisse. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15243,6 +15329,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15410,6 +15497,7 @@
           <t>narrateur|Jules pose un yaourt près de l'assiette. Le banc est lisse. On essuie une miette. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. La cuillère est à sa place. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Papa serre Jules tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15577,6 +15665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15744,6 +15833,7 @@
           <t>narrateur|Jules pose un morceau de pain près de l'assiette. Un grelot sonne. On met le doudou près. On a fait une tâche sûre, avec un adulte. Laver, poser, apporter. Le pain est sur la table. On fait une tâche sûre, avec un adulte. Laver, poser, apporter. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15911,6 +16001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15929,7 +16020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15953,6 +16044,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15967,7 +16072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16154,6 +16259,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
